--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487520_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487520_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.3915</v>
+        <v>7.2965</v>
       </c>
       <c r="E2" t="n">
-        <v>6.683</v>
+        <v>6.8018</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7085</v>
+        <v>0.4947</v>
       </c>
       <c r="G2" t="n">
         <v>2.4556</v>
@@ -610,13 +610,13 @@
         <v>1.9585</v>
       </c>
       <c r="S2" t="n">
-        <v>0.819</v>
+        <v>0.724</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4734</v>
+        <v>0.5921999999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3456</v>
+        <v>0.1317</v>
       </c>
       <c r="V2" t="n">
         <v>3.1376</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.5121</v>
+        <v>4.14</v>
       </c>
       <c r="E3" t="n">
-        <v>2.261</v>
+        <v>1.8087</v>
       </c>
       <c r="F3" t="n">
-        <v>2.2511</v>
+        <v>2.3313</v>
       </c>
       <c r="G3" t="n">
         <v>-1.6053</v>
@@ -688,13 +688,13 @@
         <v>2.3502</v>
       </c>
       <c r="S3" t="n">
-        <v>1.1803</v>
+        <v>0.8082</v>
       </c>
       <c r="T3" t="n">
-        <v>1.0369</v>
+        <v>0.5846</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1435</v>
+        <v>0.2236</v>
       </c>
       <c r="V3" t="n">
         <v>2.5869</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.0455</v>
+        <v>2.3143</v>
       </c>
       <c r="E4" t="n">
-        <v>2.4379</v>
+        <v>1.8404</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6076</v>
+        <v>0.474</v>
       </c>
       <c r="G4" t="n">
         <v>1.3346</v>
@@ -766,13 +766,13 @@
         <v>3.5253</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5096000000000001</v>
+        <v>-0.2216</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7399</v>
+        <v>0.1423</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2302</v>
+        <v>-0.3639</v>
       </c>
       <c r="V4" t="n">
         <v>-1.3448</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.308</v>
+        <v>0.0259</v>
       </c>
       <c r="E5" t="n">
-        <v>-3.1613</v>
+        <v>-2.1215</v>
       </c>
       <c r="F5" t="n">
-        <v>1.8533</v>
+        <v>2.1474</v>
       </c>
       <c r="G5" t="n">
         <v>-1.9232</v>
@@ -844,13 +844,13 @@
         <v>3.1336</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.846</v>
+        <v>-0.5121</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.4256</v>
+        <v>-0.3858</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4203</v>
+        <v>-0.1263</v>
       </c>
       <c r="V5" t="n">
         <v>-0.6724</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. KOVAC MARTINEZ</t>
+          <t>D. REY MARIÑO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.8517</v>
+        <v>-2.964</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.6968</v>
+        <v>-0.1949</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.1549</v>
+        <v>-2.7691</v>
       </c>
       <c r="G6" t="n">
-        <v>-3.0506</v>
+        <v>-0.5729</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.7413999999999999</v>
+        <v>-0.5780999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.3092</v>
+        <v>0.0052</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.9038</v>
+        <v>0.1021</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1429</v>
+        <v>0.1021</v>
       </c>
       <c r="L6" t="n">
-        <v>-2.0467</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.1468</v>
+        <v>-0.675</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.8843</v>
+        <v>-0.6802</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2625</v>
+        <v>0.0052</v>
       </c>
       <c r="P6" t="n">
-        <v>1.3709</v>
+        <v>0.9792</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3709</v>
+        <v>0.9792</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1667</v>
+        <v>-0.6618000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>0.207</v>
+        <v>-0.297</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3737</v>
+        <v>-0.3648</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.0053</v>
+        <v>-2.7086</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.0053</v>
+        <v>-2.7086</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. REY MARIÑO</t>
+          <t>A. KOVAC MARTINEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.0501</v>
+        <v>-3.1482</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2543</v>
+        <v>-2.0467</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.7958</v>
+        <v>-1.1014</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.5729</v>
+        <v>-3.0506</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.5780999999999999</v>
+        <v>-0.7413999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0052</v>
+        <v>-2.3092</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1021</v>
+        <v>-1.9038</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1021</v>
+        <v>0.1429</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>-2.0467</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.675</v>
+        <v>-1.1468</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6802</v>
+        <v>-0.8843</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0052</v>
+        <v>-0.2625</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9792</v>
+        <v>1.3709</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9792</v>
+        <v>1.3709</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7479</v>
+        <v>-0.4632</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3564</v>
+        <v>-0.1429</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3915</v>
+        <v>-0.3202</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.7086</v>
+        <v>-1.0053</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.7086</v>
+        <v>-1.0053</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.5775</v>
+        <v>-3.3089</v>
       </c>
       <c r="E8" t="n">
-        <v>-5.0791</v>
+        <v>-4.9174</v>
       </c>
       <c r="F8" t="n">
-        <v>1.5016</v>
+        <v>1.6085</v>
       </c>
       <c r="G8" t="n">
         <v>-0.0916</v>
@@ -1078,13 +1078,13 @@
         <v>2.9377</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.855</v>
+        <v>-0.5864</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6840000000000001</v>
+        <v>-0.5223</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.171</v>
+        <v>-0.0641</v>
       </c>
       <c r="V8" t="n">
         <v>-0.6724</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.4569</v>
+        <v>-4.3648</v>
       </c>
       <c r="E9" t="n">
-        <v>-5.1241</v>
+        <v>-5.0053</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6673</v>
+        <v>0.6405</v>
       </c>
       <c r="G9" t="n">
         <v>-2.4712</v>
@@ -1156,13 +1156,13 @@
         <v>2.546</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.4723</v>
+        <v>-1.3802</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.0692</v>
+        <v>-0.9504</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.403</v>
+        <v>-0.4298</v>
       </c>
       <c r="V9" t="n">
         <v>-0.1217</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.8688</v>
+        <v>-4.6743</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.3747</v>
+        <v>-4.1535</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.4941</v>
+        <v>-0.5208</v>
       </c>
       <c r="G10" t="n">
         <v>-3.5127</v>
@@ -1234,13 +1234,13 @@
         <v>1.7626</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8012</v>
+        <v>-0.6068</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.891</v>
+        <v>-0.6699000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0898</v>
+        <v>0.0631</v>
       </c>
       <c r="V10" t="n">
         <v>-1.3383</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.3924</v>
+        <v>-4.9817</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.8529</v>
+        <v>-2.2818</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.5395</v>
+        <v>-2.6999</v>
       </c>
       <c r="G11" t="n">
         <v>-0.0725</v>
@@ -1312,13 +1312,13 @@
         <v>1.9585</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5692</v>
+        <v>-0.1585</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7128</v>
+        <v>-0.1417</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1436</v>
+        <v>-0.0168</v>
       </c>
       <c r="V11" t="n">
         <v>-3.7715</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-10.5563</v>
+        <v>-9.665200000000002</v>
       </c>
       <c r="E12" t="n">
-        <v>-11.1613</v>
+        <v>-10.2702</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6051000000000006</v>
+        <v>0.6052000000000004</v>
       </c>
       <c r="G12" t="n">
         <v>-9.5098</v>
@@ -1390,13 +1390,13 @@
         <v>22.5225</v>
       </c>
       <c r="S12" t="n">
-        <v>-3.949400000000001</v>
+        <v>-3.0584</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.6818</v>
+        <v>-1.7909</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.2672</v>
+        <v>-1.2675</v>
       </c>
       <c r="V12" t="n">
         <v>-5.910500000000001</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.109999999999999</v>
+        <v>7.554</v>
       </c>
       <c r="E13" t="n">
-        <v>5.5338</v>
+        <v>4.8175</v>
       </c>
       <c r="F13" t="n">
-        <v>2.5762</v>
+        <v>2.7366</v>
       </c>
       <c r="G13" t="n">
         <v>2.9408</v>
@@ -1468,13 +1468,13 @@
         <v>1.1751</v>
       </c>
       <c r="S13" t="n">
-        <v>2.0654</v>
+        <v>1.5095</v>
       </c>
       <c r="T13" t="n">
-        <v>1.6309</v>
+        <v>0.9145</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4345</v>
+        <v>0.5949</v>
       </c>
       <c r="V13" t="n">
         <v>4.8664</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.3382</v>
+        <v>6.2488</v>
       </c>
       <c r="E14" t="n">
-        <v>5.9548</v>
+        <v>6.1594</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3834</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="G14" t="n">
         <v>5.6186</v>
@@ -1546,13 +1546,13 @@
         <v>2.1543</v>
       </c>
       <c r="S14" t="n">
-        <v>0.268</v>
+        <v>0.1786</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5058</v>
+        <v>-0.3011</v>
       </c>
       <c r="U14" t="n">
-        <v>0.7738</v>
+        <v>0.4798</v>
       </c>
       <c r="V14" t="n">
         <v>-0.7235</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.9693</v>
+        <v>3.3206</v>
       </c>
       <c r="E15" t="n">
-        <v>1.7079</v>
+        <v>2.2196</v>
       </c>
       <c r="F15" t="n">
-        <v>1.2614</v>
+        <v>1.101</v>
       </c>
       <c r="G15" t="n">
         <v>-1.0906</v>
@@ -1624,13 +1624,13 @@
         <v>1.3709</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.9609</v>
+        <v>-0.6096</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7722</v>
+        <v>-0.2605</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1887</v>
+        <v>-0.3491</v>
       </c>
       <c r="V15" t="n">
         <v>3.6498</v>
@@ -1657,10 +1657,10 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.242</v>
+        <v>2.856</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.1023</v>
+        <v>0.5118</v>
       </c>
       <c r="F16" t="n">
         <v>2.3442</v>
@@ -1702,10 +1702,10 @@
         <v>0.9792</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2617</v>
+        <v>0.8757</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4158</v>
+        <v>0.1982</v>
       </c>
       <c r="U16" t="n">
         <v>0.6775</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>K. FALL</t>
+          <t>J. MARTINEZ FERREIRO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1354</v>
+        <v>-0.3456</v>
       </c>
       <c r="E17" t="n">
-        <v>-3.6291</v>
+        <v>0.02</v>
       </c>
       <c r="F17" t="n">
-        <v>3.7646</v>
+        <v>-0.3656</v>
       </c>
       <c r="G17" t="n">
-        <v>2.7038</v>
+        <v>-0.191</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.3536</v>
+        <v>0.4104</v>
       </c>
       <c r="I17" t="n">
-        <v>4.0575</v>
+        <v>-0.6014</v>
       </c>
       <c r="J17" t="n">
-        <v>2.3435</v>
+        <v>-0.2629</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.2027</v>
+        <v>1.0208</v>
       </c>
       <c r="L17" t="n">
-        <v>2.5462</v>
+        <v>-1.2836</v>
       </c>
       <c r="M17" t="n">
-        <v>0.3603</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.151</v>
+        <v>-0.6104000000000001</v>
       </c>
       <c r="O17" t="n">
-        <v>1.5113</v>
+        <v>0.6822</v>
       </c>
       <c r="P17" t="n">
-        <v>-3.3294</v>
+        <v>0.1958</v>
       </c>
       <c r="Q17" t="n">
-        <v>-5.8755</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.546</v>
+        <v>0.1958</v>
       </c>
       <c r="S17" t="n">
-        <v>1.6447</v>
+        <v>0.2003</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2358</v>
+        <v>0.2829</v>
       </c>
       <c r="U17" t="n">
-        <v>1.4089</v>
+        <v>-0.08260000000000001</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.8837</v>
+        <v>-0.5507</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.3329</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>-0.5507</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. MARTINEZ FERREIRO</t>
+          <t>K. FALL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4037</v>
+        <v>-0.5725</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1223</v>
+        <v>-3.9361</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.526</v>
+        <v>3.3636</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.191</v>
+        <v>2.7038</v>
       </c>
       <c r="H18" t="n">
-        <v>0.4104</v>
+        <v>-1.3536</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.6014</v>
+        <v>4.0575</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.2629</v>
+        <v>2.3435</v>
       </c>
       <c r="K18" t="n">
-        <v>1.0208</v>
+        <v>-0.2027</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.2836</v>
+        <v>2.5462</v>
       </c>
       <c r="M18" t="n">
-        <v>0.07190000000000001</v>
+        <v>0.3603</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.6104000000000001</v>
+        <v>-1.151</v>
       </c>
       <c r="O18" t="n">
-        <v>0.6822</v>
+        <v>1.5113</v>
       </c>
       <c r="P18" t="n">
-        <v>0.1958</v>
+        <v>-3.3294</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-5.8755</v>
       </c>
       <c r="R18" t="n">
-        <v>0.1958</v>
+        <v>2.546</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1422</v>
+        <v>0.9368</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3852</v>
+        <v>-0.0712</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.243</v>
+        <v>1.0079</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.5507</v>
+        <v>-0.8837</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>-0.3329</v>
       </c>
       <c r="X18" t="n">
         <v>-0.5507</v>
@@ -1891,10 +1891,10 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.6253</v>
+        <v>-1.7277</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.4912</v>
+        <v>-1.5935</v>
       </c>
       <c r="F19" t="n">
         <v>-0.1341</v>
@@ -1936,10 +1936,10 @@
         <v>0.5875</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5281</v>
+        <v>0.4258</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4446</v>
+        <v>0.3423</v>
       </c>
       <c r="U19" t="n">
         <v>0.0835</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.0946</v>
+        <v>-2.09</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.5914</v>
+        <v>-3.6938</v>
       </c>
       <c r="F20" t="n">
-        <v>1.4968</v>
+        <v>1.6037</v>
       </c>
       <c r="G20" t="n">
         <v>-0.2479</v>
@@ -2014,13 +2014,13 @@
         <v>2.546</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1901</v>
+        <v>0.1947</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1764</v>
+        <v>0.0741</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0137</v>
+        <v>0.1206</v>
       </c>
       <c r="V20" t="n">
         <v>-0.6659</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.1151</v>
+        <v>-4.6874</v>
       </c>
       <c r="E21" t="n">
         <v>-5.1099</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0051</v>
+        <v>0.4226</v>
       </c>
       <c r="G21" t="n">
         <v>0.2039</v>
@@ -2092,13 +2092,13 @@
         <v>2.1543</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1901</v>
+        <v>0.2376</v>
       </c>
       <c r="T21" t="n">
         <v>0.0882</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2783</v>
+        <v>0.1494</v>
       </c>
       <c r="V21" t="n">
         <v>0.5507</v>
@@ -2128,7 +2128,7 @@
         <v>10.5562</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.6051000000000002</v>
+        <v>-0.6049999999999986</v>
       </c>
       <c r="F22" t="n">
         <v>11.1614</v>
@@ -2170,10 +2170,10 @@
         <v>13.7091</v>
       </c>
       <c r="S22" t="n">
-        <v>3.9492</v>
+        <v>3.9494</v>
       </c>
       <c r="T22" t="n">
-        <v>1.2673</v>
+        <v>1.2674</v>
       </c>
       <c r="U22" t="n">
         <v>2.6819</v>
